--- a/grupos/5APM - Estadisticos 20241.xlsx
+++ b/grupos/5APM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="96">
   <si>
     <t>Materia</t>
   </si>
@@ -203,12 +203,12 @@
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
     <t>Hernandez Alonso Antonio Ascari</t>
   </si>
   <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -221,9 +221,6 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>CAMARILLO</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
@@ -254,9 +251,6 @@
     <t>SUAREZ</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>LUNA</t>
   </si>
   <si>
@@ -282,9 +276,6 @@
   </si>
   <si>
     <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
   </si>
   <si>
     <t>GUSTAVO</t>
@@ -822,16 +813,16 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -899,16 +890,16 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -938,7 +929,7 @@
         <v>5</v>
       </c>
       <c r="U5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V5">
         <v>5</v>
@@ -976,16 +967,16 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1012,16 +1003,16 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>7</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>5</v>
@@ -1053,16 +1044,16 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1095,10 +1086,10 @@
         <v>10</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -1130,16 +1121,16 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1169,7 +1160,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1207,16 +1198,16 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1243,13 +1234,13 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9">
         <v>6</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>6</v>
@@ -1284,16 +1275,16 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -1361,16 +1352,16 @@
         <v>6</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>-1</v>
@@ -1397,10 +1388,10 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -1438,16 +1429,16 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1474,16 +1465,16 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>10</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>7</v>
@@ -1515,16 +1506,16 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1592,16 +1583,16 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1628,16 +1619,16 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>9</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -1669,16 +1660,16 @@
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -1705,16 +1696,16 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>6</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>6</v>
@@ -1746,16 +1737,16 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>-1</v>
@@ -1785,7 +1776,7 @@
         <v>9</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -1823,16 +1814,16 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -1862,13 +1853,13 @@
         <v>9</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>9</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X17">
         <v>6</v>
@@ -1900,16 +1891,16 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -1942,10 +1933,10 @@
         <v>7</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>6</v>
@@ -1977,16 +1968,16 @@
         <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>-1</v>
@@ -2016,13 +2007,13 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>6</v>
@@ -2054,16 +2045,16 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2090,7 +2081,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>10</v>
@@ -2099,7 +2090,7 @@
         <v>10</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -2131,16 +2122,16 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
         <v>-1</v>
@@ -2170,10 +2161,10 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2208,16 +2199,16 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -2244,7 +2235,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>6</v>
@@ -2285,16 +2276,16 @@
         <v>6</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>-1</v>
@@ -2321,16 +2312,16 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>6</v>
@@ -2362,16 +2353,16 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>-1</v>
@@ -2398,13 +2389,13 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>10</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -2439,16 +2430,16 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
         <v>-1</v>
@@ -2475,16 +2466,16 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>8</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2516,16 +2507,16 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
         <v>-1</v>
@@ -2552,16 +2543,16 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -2593,16 +2584,16 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>-1</v>
@@ -2629,13 +2620,13 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U27">
         <v>10</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -2670,16 +2661,16 @@
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -2706,13 +2697,13 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U28">
         <v>7</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -2747,16 +2738,16 @@
         <v>5</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>-1</v>
@@ -2786,10 +2777,10 @@
         <v>8</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>7</v>
@@ -2824,16 +2815,16 @@
         <v>6</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
         <v>-1</v>
@@ -2863,13 +2854,13 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X30">
         <v>6</v>
@@ -2901,16 +2892,16 @@
         <v>5</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
         <v>-1</v>
@@ -2943,7 +2934,7 @@
         <v>9</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>10</v>
@@ -2978,16 +2969,16 @@
         <v>5</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L32">
         <v>-1</v>
@@ -3014,13 +3005,13 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>8</v>
@@ -3055,16 +3046,16 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
         <v>-1</v>
@@ -3132,16 +3123,16 @@
         <v>7</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
         <v>-1</v>
@@ -3168,16 +3159,16 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X34">
         <v>5</v>
@@ -3209,16 +3200,16 @@
         <v>5</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
         <v>-1</v>
@@ -3245,16 +3236,16 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U35">
         <v>7</v>
       </c>
       <c r="V35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>7</v>
@@ -3286,16 +3277,16 @@
         <v>6</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L36">
         <v>-1</v>
@@ -3325,13 +3316,13 @@
         <v>9</v>
       </c>
       <c r="U36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V36">
         <v>8</v>
       </c>
       <c r="W36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X36">
         <v>6</v>
@@ -3363,16 +3354,16 @@
         <v>5</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L37">
         <v>-1</v>
@@ -3405,7 +3396,7 @@
         <v>5</v>
       </c>
       <c r="V37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W37">
         <v>6</v>
@@ -3609,16 +3600,16 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I5">
-        <v>70</v>
+        <v>78.3</v>
       </c>
       <c r="J5">
         <v>88</v>
       </c>
       <c r="K5">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="L5">
         <v>78.3</v>
@@ -3627,16 +3618,16 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O5">
-        <v>70</v>
+        <v>78.3</v>
       </c>
       <c r="P5">
         <v>88</v>
       </c>
       <c r="Q5">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="R5">
         <v>78.3</v>
@@ -3671,10 +3662,10 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J6">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K6">
         <v>100</v>
@@ -3689,10 +3680,10 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P6">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -3730,10 +3721,10 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>93.3</v>
+        <v>91.7</v>
       </c>
       <c r="J7">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K7">
         <v>100</v>
@@ -3748,10 +3739,10 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>93.3</v>
+        <v>91.7</v>
       </c>
       <c r="P7">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -3789,7 +3780,7 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -3807,7 +3798,7 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -3845,13 +3836,13 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="I9">
-        <v>73.3</v>
+        <v>81.7</v>
       </c>
       <c r="J9">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -3863,13 +3854,13 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="O9">
-        <v>73.3</v>
+        <v>81.7</v>
       </c>
       <c r="P9">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -3904,7 +3895,7 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I10">
         <v>96.7</v>
@@ -3922,7 +3913,7 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O10">
         <v>96.7</v>
@@ -3963,10 +3954,10 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J11">
         <v>92</v>
@@ -3981,10 +3972,10 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P11">
         <v>92</v>
@@ -4022,7 +4013,7 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I12">
         <v>100</v>
@@ -4040,7 +4031,7 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -4081,16 +4072,16 @@
         <v>100</v>
       </c>
       <c r="H13">
+        <v>87.5</v>
+      </c>
+      <c r="I13">
+        <v>73.3</v>
+      </c>
+      <c r="J13">
         <v>80</v>
       </c>
-      <c r="I13">
-        <v>66.7</v>
-      </c>
-      <c r="J13">
-        <v>60</v>
-      </c>
       <c r="K13">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="L13">
         <v>69.59999999999999</v>
@@ -4099,16 +4090,16 @@
         <v>100</v>
       </c>
       <c r="N13">
+        <v>87.5</v>
+      </c>
+      <c r="O13">
+        <v>73.3</v>
+      </c>
+      <c r="P13">
         <v>80</v>
       </c>
-      <c r="O13">
-        <v>66.7</v>
-      </c>
-      <c r="P13">
-        <v>60</v>
-      </c>
       <c r="Q13">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="R13">
         <v>69.59999999999999</v>
@@ -4140,10 +4131,10 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I14">
-        <v>80</v>
+        <v>88.3</v>
       </c>
       <c r="J14">
         <v>88</v>
@@ -4158,10 +4149,10 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O14">
-        <v>80</v>
+        <v>88.3</v>
       </c>
       <c r="P14">
         <v>88</v>
@@ -4202,10 +4193,10 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>93.3</v>
+        <v>95</v>
       </c>
       <c r="J15">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -4220,10 +4211,10 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>93.3</v>
+        <v>95</v>
       </c>
       <c r="P15">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4261,7 +4252,7 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J16">
         <v>100</v>
@@ -4279,7 +4270,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -4376,13 +4367,13 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I18">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J18">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K18">
         <v>100</v>
@@ -4394,13 +4385,13 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O18">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P18">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -4438,10 +4429,10 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="J19">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K19">
         <v>100</v>
@@ -4456,10 +4447,10 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="P19">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -4615,10 +4606,10 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="J22">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K22">
         <v>100</v>
@@ -4633,10 +4624,10 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P22">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -4674,7 +4665,7 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>86.7</v>
+        <v>88.3</v>
       </c>
       <c r="J23">
         <v>100</v>
@@ -4692,7 +4683,7 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>86.7</v>
+        <v>88.3</v>
       </c>
       <c r="P23">
         <v>100</v>
@@ -4733,7 +4724,7 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="J24">
         <v>100</v>
@@ -4751,7 +4742,7 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -4792,7 +4783,7 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>93.3</v>
+        <v>95</v>
       </c>
       <c r="J25">
         <v>100</v>
@@ -4810,7 +4801,7 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>93.3</v>
+        <v>95</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -4910,7 +4901,7 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>96.7</v>
+        <v>93.3</v>
       </c>
       <c r="J27">
         <v>100</v>
@@ -4928,7 +4919,7 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>96.7</v>
+        <v>93.3</v>
       </c>
       <c r="P27">
         <v>100</v>
@@ -4966,13 +4957,13 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I28">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="J28">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K28">
         <v>100</v>
@@ -4984,13 +4975,13 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O28">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="P28">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -5028,13 +5019,13 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>83.3</v>
+        <v>90</v>
       </c>
       <c r="J29">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -5046,13 +5037,13 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>83.3</v>
+        <v>90</v>
       </c>
       <c r="P29">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="Q29">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="R29">
         <v>100</v>
@@ -5084,13 +5075,13 @@
         <v>100</v>
       </c>
       <c r="H30">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I30">
-        <v>96.7</v>
+        <v>93.3</v>
       </c>
       <c r="J30">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K30">
         <v>100</v>
@@ -5102,13 +5093,13 @@
         <v>100</v>
       </c>
       <c r="N30">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O30">
-        <v>96.7</v>
+        <v>93.3</v>
       </c>
       <c r="P30">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5143,16 +5134,16 @@
         <v>100</v>
       </c>
       <c r="H31">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I31">
         <v>86.7</v>
       </c>
       <c r="J31">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="K31">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -5161,16 +5152,16 @@
         <v>100</v>
       </c>
       <c r="N31">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O31">
         <v>86.7</v>
       </c>
       <c r="P31">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="Q31">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="R31">
         <v>100</v>
@@ -5202,13 +5193,13 @@
         <v>100</v>
       </c>
       <c r="H32">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I32">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J32">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K32">
         <v>100</v>
@@ -5220,13 +5211,13 @@
         <v>100</v>
       </c>
       <c r="N32">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O32">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P32">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -5323,7 +5314,7 @@
         <v>100</v>
       </c>
       <c r="I34">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="J34">
         <v>100</v>
@@ -5341,7 +5332,7 @@
         <v>100</v>
       </c>
       <c r="O34">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P34">
         <v>100</v>
@@ -5379,16 +5370,16 @@
         <v>100</v>
       </c>
       <c r="H35">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I35">
-        <v>86.7</v>
+        <v>88.3</v>
       </c>
       <c r="J35">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K35">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="L35">
         <v>100</v>
@@ -5397,16 +5388,16 @@
         <v>100</v>
       </c>
       <c r="N35">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O35">
-        <v>86.7</v>
+        <v>88.3</v>
       </c>
       <c r="P35">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q35">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="R35">
         <v>100</v>
@@ -5438,13 +5429,13 @@
         <v>100</v>
       </c>
       <c r="H36">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I36">
         <v>100</v>
       </c>
       <c r="J36">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K36">
         <v>100</v>
@@ -5456,13 +5447,13 @@
         <v>100</v>
       </c>
       <c r="N36">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O36">
         <v>100</v>
       </c>
       <c r="P36">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q36">
         <v>100</v>
@@ -5497,16 +5488,16 @@
         <v>100</v>
       </c>
       <c r="H37">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I37">
-        <v>73.3</v>
+        <v>80</v>
       </c>
       <c r="J37">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K37">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="L37">
         <v>78.3</v>
@@ -5515,16 +5506,16 @@
         <v>100</v>
       </c>
       <c r="N37">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O37">
-        <v>73.3</v>
+        <v>80</v>
       </c>
       <c r="P37">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q37">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="R37">
         <v>78.3</v>
@@ -5660,19 +5651,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>94.09999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="G4" s="2">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5683,7 +5674,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
@@ -5692,19 +5683,19 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>94.09999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="G5" s="2">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5715,7 +5706,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
@@ -5736,7 +5727,7 @@
         <v>5.9</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5768,7 +5759,7 @@
         <v>2.9</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5818,7 +5809,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5850,16 +5841,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920153</v>
+        <v>22330051920386</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -5873,16 +5864,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920153</v>
+        <v>22330051920386</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5896,16 +5887,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920386</v>
+        <v>22330051920151</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -5919,16 +5910,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920386</v>
+        <v>22330051920158</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
         <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5942,22 +5933,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920151</v>
+        <v>22330051920162</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5965,16 +5956,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920158</v>
+        <v>22330051920299</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5988,16 +5979,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920162</v>
+        <v>22330051920170</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -6011,16 +6002,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920299</v>
+        <v>22330051920172</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
         <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -6034,16 +6025,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920170</v>
+        <v>22330051920171</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
         <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -6057,22 +6048,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920172</v>
+        <v>22330051920174</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
         <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6080,16 +6071,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920171</v>
+        <v>22330051920282</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
         <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -6098,52 +6089,6 @@
         <v>58</v>
       </c>
       <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920174</v>
-      </c>
-      <c r="B13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" t="s">
-        <v>97</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920282</v>
-      </c>
-      <c r="B14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" t="s">
-        <v>98</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5APM - Estadisticos 20241.xlsx
+++ b/grupos/5APM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="98">
   <si>
     <t>Materia</t>
   </si>
@@ -197,18 +197,21 @@
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
+    <t>Martínez Sota Luis Rey</t>
+  </si>
+  <si>
+    <t>Diaz Rodriguez Aurelio</t>
+  </si>
+  <si>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
+    <t>Hernandez Alonso Antonio Ascari</t>
   </si>
   <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
-    <t>Hernandez Alonso Antonio Ascari</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -221,85 +224,88 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CAMARILLO</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CORRO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>CORRO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>QUINTANA</t>
+  </si>
+  <si>
+    <t>PEÑA</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
   </si>
   <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
-    <t>CUAQUEHUA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
     <t>ANGUIANO</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>CARRASCO</t>
   </si>
   <si>
     <t>EVANGELISTA</t>
   </si>
   <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>CRISTIAN</t>
+  </si>
+  <si>
+    <t>ISAAC ASAEL</t>
+  </si>
+  <si>
+    <t>DINORAH AZUL</t>
+  </si>
+  <si>
+    <t>TONALLI</t>
+  </si>
+  <si>
+    <t>JULIO</t>
+  </si>
+  <si>
     <t>GUSTAVO</t>
   </si>
   <si>
-    <t>ISAAC ASAEL</t>
-  </si>
-  <si>
-    <t>MELANIE</t>
-  </si>
-  <si>
-    <t>DINORAH AZUL</t>
-  </si>
-  <si>
-    <t>TONALLI</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
     <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>STEPHANIE</t>
   </si>
   <si>
     <t>CALEB ELI</t>
@@ -828,7 +834,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -905,7 +911,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -982,7 +988,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1059,7 +1065,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1136,7 +1142,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1172,7 +1178,7 @@
         <v>6</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1213,7 +1219,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1249,7 +1255,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1290,7 +1296,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1367,7 +1373,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1444,7 +1450,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1521,7 +1527,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1557,7 +1563,7 @@
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1598,7 +1604,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1634,7 +1640,7 @@
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1675,7 +1681,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1752,7 +1758,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1788,7 +1794,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1829,7 +1835,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1865,7 +1871,7 @@
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1906,7 +1912,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1983,7 +1989,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2060,7 +2066,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2096,7 +2102,7 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2137,7 +2143,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2173,7 +2179,7 @@
         <v>6</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2214,7 +2220,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2250,7 +2256,7 @@
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2291,7 +2297,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2327,7 +2333,7 @@
         <v>6</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2368,7 +2374,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2404,7 +2410,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2445,7 +2451,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2522,7 +2528,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2558,7 +2564,7 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2599,7 +2605,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2635,7 +2641,7 @@
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2676,7 +2682,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2712,7 +2718,7 @@
         <v>5</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2753,7 +2759,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2830,7 +2836,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2866,7 +2872,7 @@
         <v>6</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2907,7 +2913,7 @@
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2943,7 +2949,7 @@
         <v>6</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2984,7 +2990,7 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3061,7 +3067,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3138,7 +3144,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3174,7 +3180,7 @@
         <v>5</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3215,7 +3221,7 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3292,7 +3298,7 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3369,7 +3375,7 @@
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3405,7 +3411,7 @@
         <v>5</v>
       </c>
       <c r="Y37">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4087,7 +4093,7 @@
         <v>69.59999999999999</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="N13">
         <v>87.5</v>
@@ -4105,7 +4111,7 @@
         <v>69.59999999999999</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -5587,19 +5593,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>67.59999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>32.4</v>
+        <v>20.6</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5741,7 +5747,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C7">
         <v>34</v>
@@ -5784,16 +5790,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -5809,7 +5815,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5818,16 +5824,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -5841,22 +5847,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920386</v>
+        <v>22330051920153</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5864,22 +5870,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920386</v>
+        <v>22330051920153</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5887,22 +5893,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920151</v>
+        <v>22330051920426</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5910,7 +5916,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920158</v>
+        <v>22330051920426</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
@@ -5919,13 +5925,13 @@
         <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5933,22 +5939,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920162</v>
+        <v>22330051920151</v>
       </c>
       <c r="B6" t="s">
         <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5956,16 +5962,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920299</v>
+        <v>22330051920162</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5979,16 +5985,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920170</v>
+        <v>22330051920299</v>
       </c>
       <c r="B8" t="s">
         <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -6002,16 +6008,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920172</v>
+        <v>22330051920170</v>
       </c>
       <c r="B9" t="s">
         <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -6025,22 +6031,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920171</v>
+        <v>22330051920386</v>
       </c>
       <c r="B10" t="s">
         <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6048,22 +6054,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920174</v>
+        <v>22330051920172</v>
       </c>
       <c r="B11" t="s">
         <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6071,24 +6077,47 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920282</v>
+        <v>22330051920174</v>
       </c>
       <c r="B12" t="s">
         <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920282</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
         <v>58</v>
       </c>
-      <c r="G12">
+      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5APM - Estadisticos 20241.xlsx
+++ b/grupos/5APM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="89">
   <si>
     <t>Materia</t>
   </si>
@@ -197,12 +197,12 @@
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
+    <t>Diaz Rodriguez Aurelio</t>
+  </si>
+  <si>
     <t>Martínez Sota Luis Rey</t>
   </si>
   <si>
-    <t>Diaz Rodriguez Aurelio</t>
-  </si>
-  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
@@ -224,15 +224,12 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
     <t>CAMARILLO</t>
   </si>
   <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
     <t>CORRO</t>
   </si>
   <si>
@@ -242,27 +239,18 @@
     <t>RAMOS</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
     <t>SUAREZ</t>
   </si>
   <si>
+    <t>QUINTANA</t>
+  </si>
+  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>QUINTANA</t>
-  </si>
-  <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -272,27 +260,18 @@
     <t>ALFONSO</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
     <t>ANGUIANO</t>
   </si>
   <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
     <t>EVANGELISTA</t>
   </si>
   <si>
+    <t>CRISTIAN</t>
+  </si>
+  <si>
     <t>MIGUEL ANGEL</t>
   </si>
   <si>
-    <t>CRISTIAN</t>
-  </si>
-  <si>
-    <t>ISAAC ASAEL</t>
-  </si>
-  <si>
     <t>DINORAH AZUL</t>
   </si>
   <si>
@@ -302,13 +281,7 @@
     <t>JULIO</t>
   </si>
   <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
     <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>CALEB ELI</t>
   </si>
   <si>
     <t>SAUL KOURCHENKOV</t>
@@ -831,7 +804,7 @@
         <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
         <v>9</v>
@@ -908,7 +881,7 @@
         <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -985,7 +958,7 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -1021,7 +994,7 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>6</v>
@@ -1062,7 +1035,7 @@
         <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -1098,7 +1071,7 @@
         <v>9</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>6</v>
@@ -1139,7 +1112,7 @@
         <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>8</v>
@@ -1175,7 +1148,7 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1216,7 +1189,7 @@
         <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -1252,7 +1225,7 @@
         <v>6</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1293,7 +1266,7 @@
         <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
         <v>10</v>
@@ -1329,7 +1302,7 @@
         <v>10</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -1370,7 +1343,7 @@
         <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>6</v>
@@ -1406,7 +1379,7 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>6</v>
@@ -1447,7 +1420,7 @@
         <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
         <v>7</v>
@@ -1483,7 +1456,7 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>8</v>
@@ -1524,7 +1497,7 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>5</v>
@@ -1601,7 +1574,7 @@
         <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>7</v>
@@ -1637,7 +1610,7 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -1678,7 +1651,7 @@
         <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
         <v>5</v>
@@ -1714,7 +1687,7 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -1755,7 +1728,7 @@
         <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
         <v>7</v>
@@ -1791,7 +1764,7 @@
         <v>10</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>7</v>
@@ -1832,7 +1805,7 @@
         <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
         <v>7</v>
@@ -1868,7 +1841,7 @@
         <v>10</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -1909,7 +1882,7 @@
         <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
         <v>6</v>
@@ -1945,7 +1918,7 @@
         <v>8</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -1986,7 +1959,7 @@
         <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>6</v>
@@ -2022,7 +1995,7 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -2063,7 +2036,7 @@
         <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -2140,7 +2113,7 @@
         <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
         <v>10</v>
@@ -2176,7 +2149,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2217,7 +2190,7 @@
         <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>6</v>
@@ -2253,7 +2226,7 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -2294,7 +2267,7 @@
         <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
         <v>8</v>
@@ -2330,7 +2303,7 @@
         <v>7</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2371,7 +2344,7 @@
         <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
         <v>8</v>
@@ -2448,7 +2421,7 @@
         <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
         <v>9</v>
@@ -2484,7 +2457,7 @@
         <v>8</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2525,7 +2498,7 @@
         <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>8</v>
@@ -2602,7 +2575,7 @@
         <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
         <v>9</v>
@@ -2679,7 +2652,7 @@
         <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
         <v>7</v>
@@ -2715,7 +2688,7 @@
         <v>7</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y28">
         <v>6</v>
@@ -2756,7 +2729,7 @@
         <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
         <v>6</v>
@@ -2792,7 +2765,7 @@
         <v>7</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>5</v>
@@ -2833,7 +2806,7 @@
         <v>7</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
         <v>8</v>
@@ -2869,7 +2842,7 @@
         <v>8</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -2910,7 +2883,7 @@
         <v>9</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
         <v>10</v>
@@ -2946,7 +2919,7 @@
         <v>10</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -2987,7 +2960,7 @@
         <v>7</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
         <v>6</v>
@@ -3064,7 +3037,7 @@
         <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M33">
         <v>10</v>
@@ -3100,7 +3073,7 @@
         <v>10</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y33">
         <v>10</v>
@@ -3141,7 +3114,7 @@
         <v>6</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
         <v>9</v>
@@ -3177,7 +3150,7 @@
         <v>7</v>
       </c>
       <c r="X34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>8</v>
@@ -3218,7 +3191,7 @@
         <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
         <v>6</v>
@@ -3254,7 +3227,7 @@
         <v>9</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y35">
         <v>5</v>
@@ -3295,7 +3268,7 @@
         <v>7</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M36">
         <v>6</v>
@@ -3331,7 +3304,7 @@
         <v>7</v>
       </c>
       <c r="X36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y36">
         <v>6</v>
@@ -3372,7 +3345,7 @@
         <v>6</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
         <v>8</v>
@@ -3618,7 +3591,7 @@
         <v>90</v>
       </c>
       <c r="L5">
-        <v>78.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="M5">
         <v>100</v>
@@ -3636,7 +3609,7 @@
         <v>90</v>
       </c>
       <c r="R5">
-        <v>78.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -4090,7 +4063,7 @@
         <v>91.7</v>
       </c>
       <c r="L13">
-        <v>69.59999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="M13">
         <v>55.6</v>
@@ -4108,7 +4081,7 @@
         <v>91.7</v>
       </c>
       <c r="R13">
-        <v>69.59999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="S13">
         <v>55.6</v>
@@ -4975,7 +4948,7 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>69.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="M28">
         <v>100</v>
@@ -4993,7 +4966,7 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>69.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -5506,7 +5479,7 @@
         <v>91.7</v>
       </c>
       <c r="L37">
-        <v>78.3</v>
+        <v>83.7</v>
       </c>
       <c r="M37">
         <v>100</v>
@@ -5524,7 +5497,7 @@
         <v>91.7</v>
       </c>
       <c r="R37">
-        <v>78.3</v>
+        <v>83.7</v>
       </c>
       <c r="S37">
         <v>100</v>
@@ -5616,7 +5589,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
@@ -5625,19 +5598,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>79.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="G3" s="2">
-        <v>20.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5648,7 +5621,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
@@ -5669,7 +5642,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5815,7 +5788,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5847,22 +5820,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920153</v>
+        <v>22330051920426</v>
       </c>
       <c r="B2" t="s">
         <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5870,22 +5843,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920153</v>
+        <v>22330051920426</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5893,22 +5866,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920426</v>
+        <v>22330051920153</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5916,22 +5889,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920426</v>
+        <v>22330051920162</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5939,22 +5912,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920151</v>
+        <v>22330051920299</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5962,16 +5935,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920162</v>
+        <v>22330051920170</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5985,16 +5958,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920299</v>
+        <v>22330051920172</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -6008,16 +5981,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920170</v>
+        <v>22330051920282</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -6026,98 +5999,6 @@
         <v>58</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920386</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D10" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920172</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920174</v>
-      </c>
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920282</v>
-      </c>
-      <c r="B13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" t="s">
-        <v>97</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5APM - Estadisticos 20241.xlsx
+++ b/grupos/5APM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="89">
   <si>
     <t>Materia</t>
   </si>
@@ -197,21 +197,21 @@
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
+    <t>Martínez Sota Luis Rey</t>
+  </si>
+  <si>
     <t>Diaz Rodriguez Aurelio</t>
   </si>
   <si>
-    <t>Martínez Sota Luis Rey</t>
+    <t>Hernandez Alonso Antonio Ascari</t>
+  </si>
+  <si>
+    <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
-    <t>Hernandez Alonso Antonio Ascari</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -224,67 +224,67 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CORRO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
     <t>VICENTE</t>
   </si>
   <si>
-    <t>CAMARILLO</t>
-  </si>
-  <si>
-    <t>CORRO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>EVANGELISTA</t>
   </si>
   <si>
     <t>QUINTANA</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>EVANGELISTA</t>
+    <t>EDUARDO EMER</t>
+  </si>
+  <si>
+    <t>DINORAH AZUL</t>
+  </si>
+  <si>
+    <t>TONALLI</t>
+  </si>
+  <si>
+    <t>JULIO</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>SAUL KOURCHENKOV</t>
   </si>
   <si>
     <t>CRISTIAN</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>DINORAH AZUL</t>
-  </si>
-  <si>
-    <t>TONALLI</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>SAUL KOURCHENKOV</t>
   </si>
 </sst>
 </file>
@@ -813,7 +813,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -890,7 +890,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -908,7 +908,7 @@
         <v>5</v>
       </c>
       <c r="U5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>5</v>
@@ -967,7 +967,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1044,7 +1044,7 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1121,7 +1121,7 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1177,7 +1177,7 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>6</v>
@@ -1198,7 +1198,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1213,7 +1213,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>6</v>
@@ -1275,7 +1275,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1352,7 +1352,7 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1370,7 +1370,7 @@
         <v>9</v>
       </c>
       <c r="U11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -1429,7 +1429,7 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1447,7 +1447,7 @@
         <v>9</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -1506,7 +1506,7 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1524,7 +1524,7 @@
         <v>5</v>
       </c>
       <c r="U13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -1583,7 +1583,7 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1601,7 +1601,7 @@
         <v>9</v>
       </c>
       <c r="U14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1660,7 +1660,7 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1737,7 +1737,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1814,7 +1814,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1891,7 +1891,7 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -1968,7 +1968,7 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2045,7 +2045,7 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2122,7 +2122,7 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2140,7 +2140,7 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>10</v>
@@ -2199,7 +2199,7 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2217,7 +2217,7 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>8</v>
@@ -2276,7 +2276,7 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2353,7 +2353,7 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2430,7 +2430,7 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2448,7 +2448,7 @@
         <v>9</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V25">
         <v>8</v>
@@ -2507,7 +2507,7 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2661,7 +2661,7 @@
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -2738,7 +2738,7 @@
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -2815,7 +2815,7 @@
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -2892,7 +2892,7 @@
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -2969,7 +2969,7 @@
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -2987,7 +2987,7 @@
         <v>7</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V32">
         <v>7</v>
@@ -3046,7 +3046,7 @@
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3102,7 +3102,7 @@
         <v>7</v>
       </c>
       <c r="H34">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I34">
         <v>8</v>
@@ -3123,7 +3123,7 @@
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3138,10 +3138,10 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>8</v>
@@ -3200,7 +3200,7 @@
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3277,7 +3277,7 @@
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3295,7 +3295,7 @@
         <v>9</v>
       </c>
       <c r="U36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V36">
         <v>8</v>
@@ -3354,7 +3354,7 @@
         <v>-1</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3372,7 +3372,7 @@
         <v>8</v>
       </c>
       <c r="U37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V37">
         <v>7</v>
@@ -3600,7 +3600,7 @@
         <v>97.5</v>
       </c>
       <c r="O5">
-        <v>78.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="P5">
         <v>88</v>
@@ -3659,7 +3659,7 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>95</v>
+        <v>95.8</v>
       </c>
       <c r="P6">
         <v>94</v>
@@ -3718,7 +3718,7 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>91.7</v>
+        <v>93.8</v>
       </c>
       <c r="P7">
         <v>96</v>
@@ -3777,7 +3777,7 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -3836,7 +3836,7 @@
         <v>92.5</v>
       </c>
       <c r="O9">
-        <v>81.7</v>
+        <v>82.3</v>
       </c>
       <c r="P9">
         <v>86</v>
@@ -3895,7 +3895,7 @@
         <v>97.5</v>
       </c>
       <c r="O10">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -3954,7 +3954,7 @@
         <v>97.5</v>
       </c>
       <c r="O11">
-        <v>95</v>
+        <v>95.8</v>
       </c>
       <c r="P11">
         <v>92</v>
@@ -4072,7 +4072,7 @@
         <v>87.5</v>
       </c>
       <c r="O13">
-        <v>73.3</v>
+        <v>81.3</v>
       </c>
       <c r="P13">
         <v>80</v>
@@ -4131,7 +4131,7 @@
         <v>90</v>
       </c>
       <c r="O14">
-        <v>88.3</v>
+        <v>91.7</v>
       </c>
       <c r="P14">
         <v>88</v>
@@ -4190,7 +4190,7 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P15">
         <v>90</v>
@@ -4249,7 +4249,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -4308,7 +4308,7 @@
         <v>100</v>
       </c>
       <c r="O17">
-        <v>96.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -4367,7 +4367,7 @@
         <v>97.5</v>
       </c>
       <c r="O18">
-        <v>98.3</v>
+        <v>92.7</v>
       </c>
       <c r="P18">
         <v>96</v>
@@ -4426,7 +4426,7 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="P19">
         <v>96</v>
@@ -4544,7 +4544,7 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -4603,7 +4603,7 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P22">
         <v>98</v>
@@ -4662,7 +4662,7 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>88.3</v>
+        <v>92.7</v>
       </c>
       <c r="P23">
         <v>100</v>
@@ -4721,7 +4721,7 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -4780,7 +4780,7 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -4898,7 +4898,7 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>93.3</v>
+        <v>91.7</v>
       </c>
       <c r="P27">
         <v>100</v>
@@ -4957,7 +4957,7 @@
         <v>97.5</v>
       </c>
       <c r="O28">
-        <v>96.7</v>
+        <v>93.8</v>
       </c>
       <c r="P28">
         <v>96</v>
@@ -5016,7 +5016,7 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="P29">
         <v>96</v>
@@ -5075,7 +5075,7 @@
         <v>97.5</v>
       </c>
       <c r="O30">
-        <v>93.3</v>
+        <v>91.7</v>
       </c>
       <c r="P30">
         <v>98</v>
@@ -5134,7 +5134,7 @@
         <v>90</v>
       </c>
       <c r="O31">
-        <v>86.7</v>
+        <v>87.5</v>
       </c>
       <c r="P31">
         <v>92</v>
@@ -5193,7 +5193,7 @@
         <v>97.5</v>
       </c>
       <c r="O32">
-        <v>98.3</v>
+        <v>94.8</v>
       </c>
       <c r="P32">
         <v>90</v>
@@ -5252,7 +5252,7 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -5311,7 +5311,7 @@
         <v>100</v>
       </c>
       <c r="O34">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P34">
         <v>100</v>
@@ -5370,7 +5370,7 @@
         <v>97.5</v>
       </c>
       <c r="O35">
-        <v>88.3</v>
+        <v>88.5</v>
       </c>
       <c r="P35">
         <v>94</v>
@@ -5429,7 +5429,7 @@
         <v>97.5</v>
       </c>
       <c r="O36">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="P36">
         <v>98</v>
@@ -5488,7 +5488,7 @@
         <v>97.5</v>
       </c>
       <c r="O37">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="P37">
         <v>98</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
@@ -5610,7 +5610,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5621,7 +5621,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
@@ -5630,19 +5630,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>91.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>8.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5653,7 +5653,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
@@ -5662,19 +5662,19 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>91.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>8.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5685,7 +5685,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
@@ -5694,19 +5694,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>94.09999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>5.9</v>
+        <v>2.9</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5717,7 +5717,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>63</v>
@@ -5726,19 +5726,19 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5788,7 +5788,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5820,7 +5820,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920426</v>
+        <v>22330051920150</v>
       </c>
       <c r="B2" t="s">
         <v>68</v>
@@ -5832,10 +5832,10 @@
         <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5843,7 +5843,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920426</v>
+        <v>22330051920150</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
@@ -5855,10 +5855,10 @@
         <v>82</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5866,19 +5866,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920153</v>
+        <v>22330051920150</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
         <v>59</v>
@@ -5889,16 +5889,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920162</v>
+        <v>22330051920150</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5912,16 +5912,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920299</v>
+        <v>22330051920162</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -5935,16 +5935,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920170</v>
+        <v>22330051920299</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5958,16 +5958,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920172</v>
+        <v>22330051920170</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -5981,16 +5981,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920282</v>
+        <v>22330051920172</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -5999,6 +5999,52 @@
         <v>58</v>
       </c>
       <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920282</v>
+      </c>
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920426</v>
+      </c>
+      <c r="B11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5APM - Estadisticos 20241.xlsx
+++ b/grupos/5APM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="77">
   <si>
     <t>Materia</t>
   </si>
@@ -194,24 +194,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Hernandez Alonso Antonio Ascari</t>
+  </si>
+  <si>
+    <t>Martínez Sota Luis Rey</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>Martínez Sota Luis Rey</t>
-  </si>
-  <si>
     <t>Diaz Rodriguez Aurelio</t>
   </si>
   <si>
-    <t>Hernandez Alonso Antonio Ascari</t>
+    <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -227,19 +227,7 @@
     <t>BAEZ</t>
   </si>
   <si>
-    <t>CORRO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
+    <t>CASTRO</t>
   </si>
   <si>
     <t>VICENTE</t>
@@ -248,19 +236,7 @@
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>EVANGELISTA</t>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>QUINTANA</t>
@@ -269,19 +245,7 @@
     <t>EDUARDO EMER</t>
   </si>
   <si>
-    <t>DINORAH AZUL</t>
-  </si>
-  <si>
-    <t>TONALLI</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>SAUL KOURCHENKOV</t>
+    <t>DIEGO</t>
   </si>
   <si>
     <t>CRISTIAN</t>
@@ -810,22 +774,22 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -840,7 +804,7 @@
         <v>10</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -887,22 +851,22 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
         <v>5</v>
@@ -914,13 +878,13 @@
         <v>5</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>5</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -964,22 +928,22 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -991,7 +955,7 @@
         <v>7</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>7</v>
@@ -1041,22 +1005,22 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1071,10 +1035,10 @@
         <v>9</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1118,22 +1082,22 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1195,40 +1159,40 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U9">
         <v>6</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1272,22 +1236,22 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1296,7 +1260,7 @@
         <v>10</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>10</v>
@@ -1349,22 +1313,22 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1426,22 +1390,22 @@
         <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>9</v>
@@ -1503,25 +1467,25 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>6</v>
@@ -1530,10 +1494,10 @@
         <v>5</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1580,25 +1544,25 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
         <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -1657,22 +1621,22 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
         <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
         <v>7</v>
@@ -1684,13 +1648,13 @@
         <v>6</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1734,22 +1698,22 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -1811,22 +1775,22 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>9</v>
@@ -1888,22 +1852,22 @@
         <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
         <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -1912,16 +1876,16 @@
         <v>7</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>8</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1965,22 +1929,22 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
         <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>8</v>
@@ -1998,7 +1962,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2042,22 +2006,22 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -2119,22 +2083,22 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2152,7 +2116,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2196,22 +2160,22 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
         <v>8</v>
@@ -2229,7 +2193,7 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2273,25 +2237,25 @@
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>8</v>
@@ -2300,7 +2264,7 @@
         <v>9</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>7</v>
@@ -2350,22 +2314,22 @@
         <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>9</v>
@@ -2427,22 +2391,22 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2460,7 +2424,7 @@
         <v>9</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2504,22 +2468,22 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
         <v>9</v>
@@ -2581,22 +2545,22 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
         <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>9</v>
@@ -2605,13 +2569,13 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>10</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>8</v>
@@ -2658,22 +2622,22 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
         <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>6</v>
@@ -2691,7 +2655,7 @@
         <v>7</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2735,22 +2699,22 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
         <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T29">
         <v>8</v>
@@ -2765,10 +2729,10 @@
         <v>7</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y29">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2812,25 +2776,25 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U30">
         <v>8</v>
@@ -2839,7 +2803,7 @@
         <v>9</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>8</v>
@@ -2889,22 +2853,22 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
         <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>8</v>
@@ -2913,7 +2877,7 @@
         <v>9</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>10</v>
@@ -2922,7 +2886,7 @@
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2966,25 +2930,25 @@
         <v>6</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O32">
         <v>8</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U32">
         <v>8</v>
@@ -2996,10 +2960,10 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3043,22 +3007,22 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3120,22 +3084,22 @@
         <v>9</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
         <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
         <v>8</v>
@@ -3197,25 +3161,25 @@
         <v>6</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O35">
         <v>7</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U35">
         <v>7</v>
@@ -3224,13 +3188,13 @@
         <v>7</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>8</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3274,22 +3238,22 @@
         <v>6</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>7</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T36">
         <v>9</v>
@@ -3298,10 +3262,10 @@
         <v>8</v>
       </c>
       <c r="V36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X36">
         <v>7</v>
@@ -3351,25 +3315,25 @@
         <v>8</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O37">
         <v>7</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U37">
         <v>6</v>
@@ -3384,7 +3348,7 @@
         <v>5</v>
       </c>
       <c r="Y37">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3597,22 +3561,22 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O5">
         <v>85.40000000000001</v>
       </c>
       <c r="P5">
-        <v>88</v>
+        <v>87.7</v>
       </c>
       <c r="Q5">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="R5">
-        <v>88.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="S5">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3662,7 +3626,7 @@
         <v>95.8</v>
       </c>
       <c r="P6">
-        <v>94</v>
+        <v>94.5</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -3721,13 +3685,13 @@
         <v>93.8</v>
       </c>
       <c r="P7">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="Q7">
         <v>100</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -3786,7 +3750,7 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -3833,13 +3797,13 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
       <c r="O9">
         <v>82.3</v>
       </c>
       <c r="P9">
-        <v>86</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -3892,13 +3856,13 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>97.5</v>
+        <v>95.2</v>
       </c>
       <c r="O10">
         <v>91.7</v>
       </c>
       <c r="P10">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -3951,13 +3915,13 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>97.5</v>
+        <v>96.8</v>
       </c>
       <c r="O11">
         <v>95.8</v>
       </c>
       <c r="P11">
-        <v>92</v>
+        <v>93.2</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -3966,7 +3930,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4010,7 +3974,7 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -4069,22 +4033,22 @@
         <v>55.6</v>
       </c>
       <c r="N13">
-        <v>87.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="O13">
         <v>81.3</v>
       </c>
       <c r="P13">
-        <v>80</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="Q13">
-        <v>91.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R13">
-        <v>79.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S13">
-        <v>55.6</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4128,13 +4092,13 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="O14">
         <v>91.7</v>
       </c>
       <c r="P14">
-        <v>88</v>
+        <v>91.8</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -4143,7 +4107,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>100</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4187,19 +4151,19 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="O15">
         <v>90.59999999999999</v>
       </c>
       <c r="P15">
-        <v>90</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="Q15">
         <v>100</v>
       </c>
       <c r="R15">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -4364,22 +4328,22 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O18">
         <v>92.7</v>
       </c>
       <c r="P18">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="Q18">
         <v>100</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4423,13 +4387,13 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O19">
         <v>95.8</v>
       </c>
       <c r="P19">
-        <v>96</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -4600,13 +4564,13 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="O22">
         <v>97.90000000000001</v>
       </c>
       <c r="P22">
-        <v>98</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -4659,19 +4623,19 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O23">
         <v>92.7</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Q23">
         <v>100</v>
       </c>
       <c r="R23">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -4777,22 +4741,22 @@
         <v>100</v>
       </c>
       <c r="N25">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O25">
         <v>90.59999999999999</v>
       </c>
       <c r="P25">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="R25">
         <v>100</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4895,13 +4859,13 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="O27">
         <v>91.7</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -4954,19 +4918,19 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O28">
         <v>93.8</v>
       </c>
       <c r="P28">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="Q28">
         <v>100</v>
       </c>
       <c r="R28">
-        <v>83.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -5019,13 +4983,13 @@
         <v>87.5</v>
       </c>
       <c r="P29">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="Q29">
-        <v>96.7</v>
+        <v>95.8</v>
       </c>
       <c r="R29">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S29">
         <v>100</v>
@@ -5072,16 +5036,16 @@
         <v>100</v>
       </c>
       <c r="N30">
-        <v>97.5</v>
+        <v>93.5</v>
       </c>
       <c r="O30">
         <v>91.7</v>
       </c>
       <c r="P30">
-        <v>98</v>
+        <v>94.5</v>
       </c>
       <c r="Q30">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R30">
         <v>100</v>
@@ -5131,16 +5095,16 @@
         <v>100</v>
       </c>
       <c r="N31">
-        <v>90</v>
+        <v>90.3</v>
       </c>
       <c r="O31">
         <v>87.5</v>
       </c>
       <c r="P31">
-        <v>92</v>
+        <v>91.8</v>
       </c>
       <c r="Q31">
-        <v>98.3</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R31">
         <v>100</v>
@@ -5190,13 +5154,13 @@
         <v>100</v>
       </c>
       <c r="N32">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O32">
         <v>94.8</v>
       </c>
       <c r="P32">
-        <v>90</v>
+        <v>93.2</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -5261,7 +5225,7 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -5308,7 +5272,7 @@
         <v>100</v>
       </c>
       <c r="N34">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O34">
         <v>97.90000000000001</v>
@@ -5317,7 +5281,7 @@
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R34">
         <v>100</v>
@@ -5367,22 +5331,22 @@
         <v>100</v>
       </c>
       <c r="N35">
-        <v>97.5</v>
+        <v>96.8</v>
       </c>
       <c r="O35">
         <v>88.5</v>
       </c>
       <c r="P35">
-        <v>94</v>
+        <v>94.5</v>
       </c>
       <c r="Q35">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="R35">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S35">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5426,13 +5390,13 @@
         <v>100</v>
       </c>
       <c r="N36">
-        <v>97.5</v>
+        <v>96.8</v>
       </c>
       <c r="O36">
         <v>93.8</v>
       </c>
       <c r="P36">
-        <v>98</v>
+        <v>97.3</v>
       </c>
       <c r="Q36">
         <v>100</v>
@@ -5485,19 +5449,19 @@
         <v>100</v>
       </c>
       <c r="N37">
-        <v>97.5</v>
+        <v>95.2</v>
       </c>
       <c r="O37">
         <v>81.3</v>
       </c>
       <c r="P37">
-        <v>98</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="Q37">
-        <v>91.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R37">
-        <v>83.7</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="S37">
         <v>100</v>
@@ -5557,7 +5521,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
@@ -5566,19 +5530,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2">
-        <v>79.40000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>20.6</v>
+        <v>5.9</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5598,16 +5562,16 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>91.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>8.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="H3">
         <v>7.6</v>
@@ -5621,7 +5585,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
@@ -5630,19 +5594,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>94.09999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>5.9</v>
+        <v>2.9</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5653,7 +5617,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
@@ -5662,16 +5626,16 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>94.09999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>5.9</v>
+        <v>2.9</v>
       </c>
       <c r="H5">
         <v>8.300000000000001</v>
@@ -5685,7 +5649,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
@@ -5694,19 +5658,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5717,7 +5681,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>63</v>
@@ -5738,7 +5702,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5788,7 +5752,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5826,16 +5790,16 @@
         <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5849,16 +5813,16 @@
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5872,10 +5836,10 @@
         <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -5889,19 +5853,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920150</v>
+        <v>21330051920112</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" t="s">
         <v>75</v>
       </c>
-      <c r="D5" t="s">
-        <v>82</v>
-      </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
         <v>58</v>
@@ -5912,22 +5876,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920162</v>
+        <v>21330051920112</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5935,116 +5899,24 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920299</v>
+        <v>22330051920426</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920170</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920172</v>
-      </c>
-      <c r="B9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920282</v>
-      </c>
-      <c r="B10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920426</v>
-      </c>
-      <c r="B11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>
